--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104645_W21.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104645_W21.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.7843</v>
+        <v>10.7139</v>
       </c>
       <c r="E2" t="n">
-        <v>5.3843</v>
+        <v>6.4073</v>
       </c>
       <c r="F2" t="n">
-        <v>4.4</v>
+        <v>4.3067</v>
       </c>
       <c r="G2" t="n">
-        <v>6.2233</v>
+        <v>6.2008</v>
       </c>
       <c r="H2" t="n">
-        <v>3.5658</v>
+        <v>3.548</v>
       </c>
       <c r="I2" t="n">
-        <v>2.6575</v>
+        <v>2.6528</v>
       </c>
       <c r="J2" t="n">
-        <v>5.8496</v>
+        <v>5.8108</v>
       </c>
       <c r="K2" t="n">
-        <v>3.0162</v>
+        <v>2.9885</v>
       </c>
       <c r="L2" t="n">
-        <v>2.8334</v>
+        <v>2.8223</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3737</v>
+        <v>0.39</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5496</v>
+        <v>0.5595</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.1759</v>
+        <v>-0.1695</v>
       </c>
       <c r="P2" t="n">
-        <v>3.8562</v>
+        <v>3.8697</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>3.8562</v>
+        <v>3.8697</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2952</v>
+        <v>0.6434</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6261</v>
+        <v>0.4387</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3309</v>
+        <v>0.2047</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="3">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.9265</v>
+        <v>8.511900000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>4.4748</v>
+        <v>4.904</v>
       </c>
       <c r="F3" t="n">
-        <v>3.4517</v>
+        <v>3.6079</v>
       </c>
       <c r="G3" t="n">
-        <v>3.5565</v>
+        <v>3.5341</v>
       </c>
       <c r="H3" t="n">
-        <v>3.7245</v>
+        <v>3.7087</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.168</v>
+        <v>-0.1746</v>
       </c>
       <c r="J3" t="n">
-        <v>3.2732</v>
+        <v>3.2296</v>
       </c>
       <c r="K3" t="n">
-        <v>3.2067</v>
+        <v>3.1781</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0665</v>
+        <v>0.0515</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2833</v>
+        <v>0.3046</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5178</v>
+        <v>0.5306</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.2345</v>
+        <v>-0.226</v>
       </c>
       <c r="P3" t="n">
-        <v>3.1757</v>
+        <v>3.1868</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>3.1757</v>
+        <v>3.1868</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1016</v>
+        <v>0.7014</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1089</v>
+        <v>0.5849</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0073</v>
+        <v>0.1165</v>
       </c>
       <c r="V3" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W3" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.9952</v>
+        <v>5.6665</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7641</v>
+        <v>2.2184</v>
       </c>
       <c r="F4" t="n">
-        <v>3.2311</v>
+        <v>3.4481</v>
       </c>
       <c r="G4" t="n">
-        <v>1.0372</v>
+        <v>1.0222</v>
       </c>
       <c r="H4" t="n">
-        <v>3.8094</v>
+        <v>3.8084</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.7723</v>
+        <v>-2.7862</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8952</v>
+        <v>0.8611</v>
       </c>
       <c r="K4" t="n">
-        <v>2.9612</v>
+        <v>2.9475</v>
       </c>
       <c r="L4" t="n">
-        <v>-2.066</v>
+        <v>-2.0864</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1419</v>
+        <v>0.1611</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8483000000000001</v>
+        <v>0.8609</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.7063</v>
+        <v>-0.6998</v>
       </c>
       <c r="P4" t="n">
-        <v>3.4025</v>
+        <v>3.4145</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>3.4025</v>
+        <v>3.4145</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.9908</v>
+        <v>0.6851</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6775</v>
+        <v>0.8126</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3133</v>
+        <v>-0.1275</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.7906</v>
+        <v>2.5275</v>
       </c>
       <c r="E5" t="n">
-        <v>3.4786</v>
+        <v>2.2805</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3121</v>
+        <v>0.247</v>
       </c>
       <c r="G5" t="n">
-        <v>1.2917</v>
+        <v>1.283</v>
       </c>
       <c r="H5" t="n">
-        <v>1.8515</v>
+        <v>1.8415</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5598</v>
+        <v>-0.5586</v>
       </c>
       <c r="J5" t="n">
-        <v>1.0484</v>
+        <v>1.0233</v>
       </c>
       <c r="K5" t="n">
-        <v>1.6482</v>
+        <v>1.6268</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.5998</v>
+        <v>-0.6035</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2433</v>
+        <v>0.2597</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2033</v>
+        <v>0.2148</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04</v>
+        <v>0.0449</v>
       </c>
       <c r="P5" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S5" t="n">
-        <v>3.482</v>
+        <v>2.217</v>
       </c>
       <c r="T5" t="n">
-        <v>2.8158</v>
+        <v>1.6441</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6663</v>
+        <v>0.5729</v>
       </c>
       <c r="V5" t="n">
-        <v>-2.571</v>
+        <v>-2.5659</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.3856</v>
+        <v>-0.387</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Y. KRAAG</t>
+          <t>R. RUBIO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.7538</v>
+        <v>2.2311</v>
       </c>
       <c r="E6" t="n">
-        <v>1.6971</v>
+        <v>1.402</v>
       </c>
       <c r="F6" t="n">
-        <v>1.0567</v>
+        <v>0.8290999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>-3.4478</v>
+        <v>-0.7284</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.6535</v>
+        <v>0.0433</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7944</v>
+        <v>-0.7717000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>-2.3716</v>
+        <v>0.1014</v>
       </c>
       <c r="K6" t="n">
-        <v>-3.1872</v>
+        <v>0.4891</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8156</v>
+        <v>-0.3877</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.0762</v>
+        <v>-0.8298</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5337</v>
+        <v>-0.4458</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.6099</v>
+        <v>-0.384</v>
       </c>
       <c r="P6" t="n">
-        <v>3.4025</v>
+        <v>0.2276</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R6" t="n">
-        <v>3.4025</v>
+        <v>1.3658</v>
       </c>
       <c r="S6" t="n">
-        <v>2.7991</v>
+        <v>0.7107</v>
       </c>
       <c r="T6" t="n">
-        <v>2.9761</v>
+        <v>0.2598</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1769</v>
+        <v>0.4509</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>2.0212</v>
       </c>
       <c r="W6" t="n">
-        <v>1.0927</v>
+        <v>2.1789</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.0927</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="7">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.1442</v>
+        <v>1.5357</v>
       </c>
       <c r="E7" t="n">
-        <v>2.9255</v>
+        <v>2.2143</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.7814</v>
+        <v>-0.6786</v>
       </c>
       <c r="G7" t="n">
-        <v>1.4442</v>
+        <v>1.4418</v>
       </c>
       <c r="H7" t="n">
-        <v>1.2496</v>
+        <v>1.2466</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1946</v>
+        <v>0.1952</v>
       </c>
       <c r="J7" t="n">
-        <v>1.4919</v>
+        <v>1.4851</v>
       </c>
       <c r="K7" t="n">
-        <v>1.4546</v>
+        <v>1.4479</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.0477</v>
+        <v>-0.0433</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.205</v>
+        <v>-0.2012</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S7" t="n">
-        <v>1.3389</v>
+        <v>0.7281</v>
       </c>
       <c r="T7" t="n">
-        <v>1.4336</v>
+        <v>0.7292</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.09470000000000001</v>
+        <v>-0.0011</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. BIRGANDER</t>
+          <t>Y. KRAAG</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.7494</v>
+        <v>1.216</v>
       </c>
       <c r="E8" t="n">
-        <v>1.4117</v>
+        <v>-0.0298</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3377</v>
+        <v>1.2458</v>
       </c>
       <c r="G8" t="n">
-        <v>2.3057</v>
+        <v>-3.4606</v>
       </c>
       <c r="H8" t="n">
-        <v>3.0333</v>
+        <v>-2.662</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.7276</v>
+        <v>-0.7986</v>
       </c>
       <c r="J8" t="n">
-        <v>2.316</v>
+        <v>-2.4032</v>
       </c>
       <c r="K8" t="n">
-        <v>2.2787</v>
+        <v>-3.207</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0373</v>
+        <v>0.8038999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0104</v>
+        <v>-1.0574</v>
       </c>
       <c r="N8" t="n">
-        <v>0.7546</v>
+        <v>0.5451</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.7649</v>
+        <v>-1.6025</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>3.4145</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1342</v>
+        <v>3.4145</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6971000000000001</v>
+        <v>1.2621</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2299</v>
+        <v>1.2839</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4673</v>
+        <v>-0.0218</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.2534</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2534</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. RUBIO</t>
+          <t>S. BIRGANDER</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.6806</v>
+        <v>1.194</v>
       </c>
       <c r="E9" t="n">
-        <v>1.1295</v>
+        <v>0.9883</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5511</v>
+        <v>0.2057</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.7227</v>
+        <v>2.3029</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0477</v>
+        <v>3.022</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.7703</v>
+        <v>-0.7191</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1267</v>
+        <v>2.2985</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5053</v>
+        <v>2.2613</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.3786</v>
+        <v>0.0372</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.8494</v>
+        <v>0.0044</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4576</v>
+        <v>0.7608</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.3918</v>
+        <v>-0.7563</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2268</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R9" t="n">
-        <v>1.361</v>
+        <v>1.1382</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1518</v>
+        <v>0.1383</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0484</v>
+        <v>-0.1721</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2002</v>
+        <v>0.3104</v>
       </c>
       <c r="V9" t="n">
-        <v>2.0246</v>
+        <v>-1.2472</v>
       </c>
       <c r="W9" t="n">
-        <v>2.1853</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1607</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. TOMIC</t>
+          <t>J. PARKER</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2083</v>
+        <v>0.25</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0207</v>
+        <v>-1.0631</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1876</v>
+        <v>1.3131</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.7478</v>
+        <v>-0.0184</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.0921</v>
+        <v>1.8704</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.6556999999999999</v>
+        <v>-1.8888</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.4852</v>
+        <v>0.4667</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6345</v>
+        <v>1.9715</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1493</v>
+        <v>-1.5048</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.2626</v>
+        <v>-0.4851</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4576</v>
+        <v>-0.1011</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.805</v>
+        <v>-0.384</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6805</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R10" t="n">
-        <v>2.9488</v>
+        <v>1.1382</v>
       </c>
       <c r="S10" t="n">
-        <v>1.8219</v>
+        <v>0.8618</v>
       </c>
       <c r="T10" t="n">
-        <v>1.6816</v>
+        <v>0.2018</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1403</v>
+        <v>0.66</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="W10" t="n">
-        <v>1.0927</v>
+        <v>0.5447</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.639</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,58 +1267,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1336</v>
+        <v>0.006</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.6982</v>
+        <v>-0.8505</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8318</v>
+        <v>0.8566</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.6014</v>
+        <v>-0.614</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3983</v>
+        <v>0.3964</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.9997</v>
+        <v>-1.0104</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7625</v>
+        <v>0.7317</v>
       </c>
       <c r="K11" t="n">
-        <v>0.9973</v>
+        <v>0.9858</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.2347</v>
+        <v>-0.2541</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.3639</v>
+        <v>-1.3457</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.599</v>
+        <v>-0.5893</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.7649</v>
+        <v>-0.7563</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R11" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S11" t="n">
-        <v>1.1886</v>
+        <v>1.0753</v>
       </c>
       <c r="T11" t="n">
-        <v>0.8075</v>
+        <v>0.6941000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3811</v>
+        <v>0.3812</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. PARKER</t>
+          <t>A. TOMIC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.3803</v>
+        <v>-0.3884</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.9212</v>
+        <v>-0.4805</v>
       </c>
       <c r="F12" t="n">
-        <v>1.5409</v>
+        <v>0.0921</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.0066</v>
+        <v>-1.7573</v>
       </c>
       <c r="H12" t="n">
-        <v>1.8833</v>
+        <v>-1.105</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.8899</v>
+        <v>-0.6523</v>
       </c>
       <c r="J12" t="n">
-        <v>0.4965</v>
+        <v>-0.5103</v>
       </c>
       <c r="K12" t="n">
-        <v>1.9945</v>
+        <v>-0.6592</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.4981</v>
+        <v>0.1489</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.503</v>
+        <v>-1.2471</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.1113</v>
+        <v>-0.4458</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.3918</v>
+        <v>-0.8012</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.1342</v>
+        <v>0.6829</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R12" t="n">
-        <v>1.1342</v>
+        <v>2.9592</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2141</v>
+        <v>1.2308</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6956</v>
+        <v>1.2166</v>
       </c>
       <c r="U12" t="n">
-        <v>0.9097</v>
+        <v>0.0141</v>
       </c>
       <c r="V12" t="n">
-        <v>0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W12" t="n">
-        <v>0.5463</v>
+        <v>1.0895</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.0184</v>
+        <v>-2.3669</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.1844</v>
+        <v>-1.4861</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.834</v>
+        <v>-0.8808</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.1588</v>
+        <v>-2.1626</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.567</v>
+        <v>-1.5681</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.5918</v>
+        <v>-0.5945</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.9062</v>
+        <v>-1.918</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.1571</v>
+        <v>-1.1656</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.749</v>
+        <v>-0.7524</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.2526</v>
+        <v>-0.2446</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.4099</v>
+        <v>-0.4025</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="P13" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2867</v>
+        <v>0.36</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2782</v>
+        <v>0.4319</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.008500000000000001</v>
+        <v>-0.07190000000000001</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>30.76780000000001</v>
+        <v>31.0973</v>
       </c>
       <c r="E14" t="n">
-        <v>16.4825</v>
+        <v>16.5048</v>
       </c>
       <c r="F14" t="n">
-        <v>14.2853</v>
+        <v>14.5927</v>
       </c>
       <c r="G14" t="n">
-        <v>7.173499999999999</v>
+        <v>7.043499999999998</v>
       </c>
       <c r="H14" t="n">
-        <v>14.2508</v>
+        <v>14.1502</v>
       </c>
       <c r="I14" t="n">
-        <v>-7.0774</v>
+        <v>-7.1068</v>
       </c>
       <c r="J14" t="n">
-        <v>11.497</v>
+        <v>11.1767</v>
       </c>
       <c r="K14" t="n">
-        <v>13.0839</v>
+        <v>12.8647</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.5868</v>
+        <v>-1.6879</v>
       </c>
       <c r="M14" t="n">
-        <v>-4.323600000000001</v>
+        <v>-4.1332</v>
       </c>
       <c r="N14" t="n">
-        <v>1.166900000000001</v>
+        <v>1.286</v>
       </c>
       <c r="O14" t="n">
-        <v>-5.490399999999999</v>
+        <v>-5.418900000000001</v>
       </c>
       <c r="P14" t="n">
-        <v>15.8783</v>
+        <v>15.9341</v>
       </c>
       <c r="Q14" t="n">
-        <v>-9.0733</v>
+        <v>-9.1053</v>
       </c>
       <c r="R14" t="n">
-        <v>24.9518</v>
+        <v>25.0396</v>
       </c>
       <c r="S14" t="n">
-        <v>10.2224</v>
+        <v>10.614</v>
       </c>
       <c r="T14" t="n">
-        <v>7.727599999999999</v>
+        <v>8.125499999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>2.4951</v>
+        <v>2.4884</v>
       </c>
       <c r="V14" t="n">
-        <v>-2.5069</v>
+        <v>-2.494400000000001</v>
       </c>
       <c r="W14" t="n">
-        <v>6.331099999999999</v>
+        <v>6.307599999999999</v>
       </c>
       <c r="X14" t="n">
-        <v>-8.837899999999999</v>
+        <v>-8.802099999999999</v>
       </c>
     </row>
     <row r="15">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.2493</v>
+        <v>-0.078</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4801</v>
+        <v>0.6871</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.7294</v>
+        <v>-0.7651</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.6066</v>
+        <v>-1.5996</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.7345</v>
+        <v>-1.7293</v>
       </c>
       <c r="I15" t="n">
-        <v>0.128</v>
+        <v>0.1297</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1246</v>
+        <v>0.1065</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.3952</v>
+        <v>-0.4072</v>
       </c>
       <c r="L15" t="n">
-        <v>0.5197000000000001</v>
+        <v>0.5135999999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.7311</v>
+        <v>-1.7061</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.3393</v>
+        <v>-1.3221</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.3918</v>
+        <v>-0.384</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R15" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.8280999999999999</v>
+        <v>-0.6573</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6956</v>
+        <v>-0.4601</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1325</v>
+        <v>-0.1972</v>
       </c>
       <c r="V15" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="W15" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.8051</v>
+        <v>-0.5774</v>
       </c>
       <c r="E16" t="n">
-        <v>0.7889</v>
+        <v>1.1037</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.594</v>
+        <v>-1.6811</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1324</v>
+        <v>0.1409</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.9019</v>
+        <v>-0.8991</v>
       </c>
       <c r="I16" t="n">
-        <v>1.0343</v>
+        <v>1.04</v>
       </c>
       <c r="J16" t="n">
-        <v>1.9616</v>
+        <v>1.9308</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3597</v>
+        <v>0.3373</v>
       </c>
       <c r="L16" t="n">
-        <v>1.6019</v>
+        <v>1.5935</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.8292</v>
+        <v>-1.7899</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.2615</v>
+        <v>-1.2364</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.5676</v>
+        <v>-0.5535</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="R16" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.0135</v>
+        <v>-0.7883</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6775</v>
+        <v>-0.3232</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.336</v>
+        <v>-0.4651</v>
       </c>
       <c r="V16" t="n">
-        <v>0.9834000000000001</v>
+        <v>0.9805</v>
       </c>
       <c r="W16" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1093</v>
+        <v>-0.1089</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. BRIMAH</t>
+          <t>J. ROUSSELLE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.2356</v>
+        <v>-0.6994</v>
       </c>
       <c r="E17" t="n">
-        <v>1.1757</v>
+        <v>2.8627</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.4113</v>
+        <v>-3.5621</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6898</v>
+        <v>0.7537</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5351</v>
+        <v>-3.3756</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1547</v>
+        <v>4.1294</v>
       </c>
       <c r="J17" t="n">
-        <v>1.4773</v>
+        <v>3.4648</v>
       </c>
       <c r="K17" t="n">
-        <v>1.4027</v>
+        <v>-0.6313</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0746</v>
+        <v>4.0961</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.7875</v>
+        <v>-2.7111</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.8675</v>
+        <v>-2.7444</v>
       </c>
       <c r="O17" t="n">
-        <v>0.08</v>
+        <v>0.0333</v>
       </c>
       <c r="P17" t="n">
-        <v>-2.4952</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.722</v>
+        <v>-1.3658</v>
       </c>
       <c r="R17" t="n">
-        <v>0.2268</v>
+        <v>1.1382</v>
       </c>
       <c r="S17" t="n">
-        <v>1.0646</v>
+        <v>-1.3832</v>
       </c>
       <c r="T17" t="n">
-        <v>2.099</v>
+        <v>-0.4835</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.0344</v>
+        <v>-0.8997000000000001</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.4949</v>
+        <v>0.1578</v>
       </c>
       <c r="W17" t="n">
-        <v>0.3214</v>
+        <v>1.2472</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.8163</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. ROUSSELLE</t>
+          <t>P. TOMAS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.5896</v>
+        <v>-1.4643</v>
       </c>
       <c r="E18" t="n">
-        <v>2.4212</v>
+        <v>-0.8258</v>
       </c>
       <c r="F18" t="n">
-        <v>-4.0109</v>
+        <v>-0.6384</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7336</v>
+        <v>-1.4956</v>
       </c>
       <c r="H18" t="n">
-        <v>-3.3927</v>
+        <v>-0.6867</v>
       </c>
       <c r="I18" t="n">
-        <v>4.1263</v>
+        <v>-0.8089</v>
       </c>
       <c r="J18" t="n">
-        <v>3.4845</v>
+        <v>-0.7352</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.6203</v>
+        <v>0.0172</v>
       </c>
       <c r="L18" t="n">
-        <v>4.1048</v>
+        <v>-0.7524</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.7509</v>
+        <v>-0.7604</v>
       </c>
       <c r="N18" t="n">
-        <v>-2.7724</v>
+        <v>-0.7039</v>
       </c>
       <c r="O18" t="n">
-        <v>0.0214</v>
+        <v>-0.0565</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.361</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1342</v>
+        <v>0.2276</v>
       </c>
       <c r="S18" t="n">
-        <v>-2.2571</v>
+        <v>-0.1963</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.9557</v>
+        <v>-0.0907</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.3014</v>
+        <v>-0.1057</v>
       </c>
       <c r="V18" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.2534</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. TOMAS</t>
+          <t>L. COSTA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.6172</v>
+        <v>-1.95</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.9404</v>
+        <v>0.3221</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.6768</v>
+        <v>-2.2721</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.4989</v>
+        <v>-0.9842</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.6912</v>
+        <v>-2.7896</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.8077</v>
+        <v>1.8053</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.7317</v>
+        <v>0.2201</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0173</v>
+        <v>-1.1796</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.749</v>
+        <v>1.3997</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.7672</v>
+        <v>-1.2043</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.7086</v>
+        <v>-1.61</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.0586</v>
+        <v>0.4057</v>
       </c>
       <c r="P19" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.3658</v>
       </c>
       <c r="R19" t="n">
-        <v>0.2268</v>
+        <v>1.5934</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3451</v>
+        <v>-2.174</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2087</v>
+        <v>-0.7112000000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1364</v>
+        <v>-1.4628</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.9805</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.1789</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.1984</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>B. OLUMUYIWA</t>
+          <t>A. BRIMAH</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.8425</v>
+        <v>-2.3642</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.0687</v>
+        <v>-0.1397</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2261</v>
+        <v>-2.2246</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.0133</v>
+        <v>0.7122000000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.2208</v>
+        <v>0.5479000000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>1.2076</v>
+        <v>0.1643</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.4208</v>
+        <v>1.4707</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.6447000000000001</v>
+        <v>1.3962</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2239</v>
+        <v>0.0745</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.5924</v>
+        <v>-0.7585</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.5761</v>
+        <v>-0.8483000000000001</v>
       </c>
       <c r="O20" t="n">
-        <v>0.9837</v>
+        <v>0.0898</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.6805</v>
+        <v>-2.5039</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.2683</v>
+        <v>-2.7316</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5878</v>
+        <v>0.2276</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1488</v>
+        <v>-0.0765</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4597</v>
+        <v>0.8057</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6085</v>
+        <v>-0.8823</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.4959</v>
       </c>
       <c r="W20" t="n">
-        <v>0.1607</v>
+        <v>0.3155</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.1607</v>
+        <v>-0.8114</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>L. COSTA</t>
+          <t>B. OLUMUYIWA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.4558</v>
+        <v>-2.7153</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.1098</v>
+        <v>-3.0411</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.346</v>
+        <v>0.3258</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.9967</v>
+        <v>-0.9988</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.8039</v>
+        <v>-2.2147</v>
       </c>
       <c r="I21" t="n">
-        <v>1.8072</v>
+        <v>1.2159</v>
       </c>
       <c r="J21" t="n">
-        <v>0.2484</v>
+        <v>-0.4391</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.1642</v>
+        <v>-0.6625</v>
       </c>
       <c r="L21" t="n">
-        <v>1.4126</v>
+        <v>0.2234</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.2451</v>
+        <v>-0.5598</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.6397</v>
+        <v>-1.5522</v>
       </c>
       <c r="O21" t="n">
-        <v>0.3946</v>
+        <v>0.9925</v>
       </c>
       <c r="P21" t="n">
-        <v>0.2268</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.361</v>
+        <v>-2.2763</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S21" t="n">
-        <v>-2.6694</v>
+        <v>-1.0336</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.1825</v>
+        <v>-0.4835</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.4868</v>
+        <v>-0.5501</v>
       </c>
       <c r="V21" t="n">
-        <v>0.9834000000000001</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>2.1853</v>
+        <v>0.1578</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2019</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="22">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.5156</v>
+        <v>-5.8601</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.5345</v>
+        <v>-4.1017</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.9811</v>
+        <v>-1.7585</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.7615</v>
+        <v>-2.7581</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.7721</v>
+        <v>-2.7607</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0106</v>
+        <v>0.0026</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.135</v>
+        <v>-1.1654</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.3779</v>
+        <v>-0.3899</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.7572</v>
+        <v>-0.7754</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.6265</v>
+        <v>-1.5927</v>
       </c>
       <c r="N22" t="n">
-        <v>-2.3942</v>
+        <v>-2.3708</v>
       </c>
       <c r="O22" t="n">
-        <v>0.7678</v>
+        <v>0.778</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.6199</v>
+        <v>-0.9639</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9043</v>
+        <v>-0.4324</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7156</v>
+        <v>-0.5315</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.5965</v>
+        <v>-6.8961</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.8072</v>
+        <v>-3.9604</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.7893</v>
+        <v>-2.9357</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.5013</v>
+        <v>-2.4798</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.1229</v>
+        <v>-2.1061</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.3785</v>
+        <v>-0.3737</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.0135</v>
+        <v>-1.0334</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.6722</v>
+        <v>-0.6830000000000001</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.3413</v>
+        <v>-0.3505</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.4878</v>
+        <v>-1.4464</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.4506</v>
+        <v>-1.4232</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.0372</v>
+        <v>-0.0232</v>
       </c>
       <c r="P23" t="n">
-        <v>-3.1757</v>
+        <v>-3.1868</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.8562</v>
+        <v>-3.8697</v>
       </c>
       <c r="R23" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8103</v>
+        <v>-1.1205</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0302</v>
+        <v>-0.1467</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.78</v>
+        <v>-0.9738</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.1093</v>
+        <v>-0.1089</v>
       </c>
       <c r="W23" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.2019</v>
+        <v>-1.1984</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.8605</v>
+        <v>-7.3543</v>
       </c>
       <c r="E24" t="n">
-        <v>-7.6906</v>
+        <v>-7.4994</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.1699</v>
+        <v>0.1451</v>
       </c>
       <c r="G24" t="n">
-        <v>1.6489</v>
+        <v>1.6657</v>
       </c>
       <c r="H24" t="n">
-        <v>1.854</v>
+        <v>1.8635</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.2052</v>
+        <v>-0.1978</v>
       </c>
       <c r="J24" t="n">
-        <v>0.3282</v>
+        <v>0.3133</v>
       </c>
       <c r="K24" t="n">
-        <v>0.928</v>
+        <v>0.9167999999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.5998</v>
+        <v>-0.6035</v>
       </c>
       <c r="M24" t="n">
-        <v>1.3206</v>
+        <v>1.3523</v>
       </c>
       <c r="N24" t="n">
-        <v>0.926</v>
+        <v>0.9467</v>
       </c>
       <c r="O24" t="n">
-        <v>0.3946</v>
+        <v>0.4057</v>
       </c>
       <c r="P24" t="n">
-        <v>-7.2586</v>
+        <v>-7.2842</v>
       </c>
       <c r="Q24" t="n">
-        <v>-8.166</v>
+        <v>-8.194699999999999</v>
       </c>
       <c r="R24" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.5951</v>
+        <v>-1.0821</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3992</v>
+        <v>-0.1628</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.1959</v>
+        <v>-0.9193</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.6556</v>
+        <v>-0.6536999999999999</v>
       </c>
       <c r="W24" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.2019</v>
+        <v>-1.1984</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-30.7677</v>
+        <v>-29.9591</v>
       </c>
       <c r="E25" t="n">
-        <v>-14.2853</v>
+        <v>-14.5925</v>
       </c>
       <c r="F25" t="n">
-        <v>-16.4826</v>
+        <v>-15.3667</v>
       </c>
       <c r="G25" t="n">
-        <v>-7.1736</v>
+        <v>-7.043599999999999</v>
       </c>
       <c r="H25" t="n">
-        <v>-14.2509</v>
+        <v>-14.1504</v>
       </c>
       <c r="I25" t="n">
-        <v>7.0773</v>
+        <v>7.1068</v>
       </c>
       <c r="J25" t="n">
-        <v>4.3236</v>
+        <v>4.133099999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.1668</v>
+        <v>-1.286</v>
       </c>
       <c r="L25" t="n">
-        <v>5.4902</v>
+        <v>5.419</v>
       </c>
       <c r="M25" t="n">
-        <v>-11.4971</v>
+        <v>-11.1769</v>
       </c>
       <c r="N25" t="n">
-        <v>-13.0839</v>
+        <v>-12.8646</v>
       </c>
       <c r="O25" t="n">
-        <v>1.5869</v>
+        <v>1.6878</v>
       </c>
       <c r="P25" t="n">
-        <v>-15.8783</v>
+        <v>-15.9341</v>
       </c>
       <c r="Q25" t="n">
-        <v>-24.9517</v>
+        <v>-25.0394</v>
       </c>
       <c r="R25" t="n">
-        <v>9.0732</v>
+        <v>9.1052</v>
       </c>
       <c r="S25" t="n">
-        <v>-10.2227</v>
+        <v>-9.4757</v>
       </c>
       <c r="T25" t="n">
-        <v>-2.495</v>
+        <v>-2.4884</v>
       </c>
       <c r="U25" t="n">
-        <v>-7.7275</v>
+        <v>-6.9875</v>
       </c>
       <c r="V25" t="n">
-        <v>2.506699999999999</v>
+        <v>2.4945</v>
       </c>
       <c r="W25" t="n">
-        <v>8.837800000000001</v>
+        <v>8.802</v>
       </c>
       <c r="X25" t="n">
-        <v>-6.331</v>
+        <v>-6.307499999999999</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104645_W21.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104645_W21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104645_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104645_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104645_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104645_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104645_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104645_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104645_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104645_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104645_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104645_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104645_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104645_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-8.802099999999999</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104645_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-0.1089</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104645_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104645_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104645_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.1984</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104645_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-0.8114</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104645_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104645_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104645_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-1.1984</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104645_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-1.1984</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104645_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,7 @@
       <c r="X25" t="n">
         <v>-6.307499999999999</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
